--- a/request_forms/042_role_closure_confirmation_request_form--request_forms.xlsx
+++ b/request_forms/042_role_closure_confirmation_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'form_type',_'value':_'form_type'}</t>
+          <t>form_type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Form Type', 'value': 'Form Type'}</t>
+          <t>Form Type</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'hr',_'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'HR', 'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'IT', 'value': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_choices</t>
+          <t>form_1_confirmed_location_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1335,274 +1335,274 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_3_choices</t>
+          <t>form_1_confirmed_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_3_choices</t>
+          <t>form_1_confirmed_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_1_confirmed_choices</t>
+          <t>form_1_confirmed_location_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_1_confirmed_choices</t>
+          <t>form_1_confirmed_location_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_1_confirmed_choices</t>
+          <t>form_1_confirmed_location_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_4_choices</t>
+          <t>form_1_confirmed_location_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_4_choices</t>
+          <t>form_1_confirmed_location_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_4_choices</t>
+          <t>form_1_confirmed_location_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_5_choices</t>
+          <t>form_1_confirmed_location_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_5_choices</t>
+          <t>form_1_confirmed_location_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_6_choices</t>
+          <t>form_1_confirmed_location_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_6_choices</t>
+          <t>form_1_confirmed_location_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_7_choices</t>
+          <t>form_1_confirmed_location_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_7_choices</t>
+          <t>form_1_confirmed_location_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_8_choices</t>
+          <t>form_1_confirmed_location_10_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'los_angeles',_'value':_'los_angeles'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Los Angeles', 'value': 'Los Angeles'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_1_confirmed_location_8_choices</t>
+          <t>form_1_confirmed_location_10_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1611,74 +1611,6 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>form_1_confirmed_location_9_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>form_1_confirmed_location_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_1_confirmed_location_10_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'new_york',_'value':_'new_york'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'New York', 'value': 'New York'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>form_1_confirmed_location_10_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
